--- a/NY_State_Reports_2026-10-23/Rush_Street_Interactive_Weekly_Report.xlsx
+++ b/NY_State_Reports_2026-10-23/Rush_Street_Interactive_Weekly_Report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\MOBILE SPORTS WAGERING\11_Weekly Web Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41ABAB10-BAEA-46BB-B68E-53468EC66848}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09944DFD-32FB-4C8B-A3E9-4C11E1CF1EF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EDA5EF8F-B63B-4D9E-966F-AB4A019BBE74}"/>
   </bookViews>
@@ -393,7 +393,12 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color theme="0"/>
@@ -2890,7 +2895,12 @@
         <v>46313</v>
       </c>
       <c r="B42" s="20"/>
-      <c r="F42" s="23"/>
+      <c r="C42" s="21">
+        <v>10455699.010000002</v>
+      </c>
+      <c r="F42" s="23">
+        <v>602300.1100000001</v>
+      </c>
       <c r="G42"/>
       <c r="H42"/>
       <c r="I42"/>
@@ -3411,11 +3421,11 @@
       </c>
       <c r="C67" s="24">
         <f>SUM(C13:C66)</f>
-        <v>286909453.62999994</v>
+        <v>297365152.63999993</v>
       </c>
       <c r="F67" s="34">
         <f>SUM(F13:F66)</f>
-        <v>24074836.960000001</v>
+        <v>24677137.07</v>
       </c>
       <c r="G67"/>
       <c r="H67"/>
@@ -5081,7 +5091,7 @@
     <mergeCell ref="A72:J72"/>
   </mergeCells>
   <conditionalFormatting sqref="F18">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17469,7 +17479,7 @@
     <mergeCell ref="A72:J72"/>
   </mergeCells>
   <conditionalFormatting sqref="C13:E13 F13:F16 E14:E16 C14:D25 E17:F25">
-    <cfRule type="cellIs" dxfId="2" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21584,12 +21594,12 @@
     <mergeCell ref="A70:J70"/>
   </mergeCells>
   <conditionalFormatting sqref="C13:E13 F13:F16 E14:E16 C14:D34 E17:F34">
-    <cfRule type="cellIs" dxfId="1" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="7" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C35:F64">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
